--- a/back/debug_export.xlsx
+++ b/back/debug_export.xlsx
@@ -14,21 +14,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>Bob</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t>Дата измерения</t>
+  </si>
+  <si>
+    <t>Дней эксплуатации</t>
+  </si>
+  <si>
+    <t>Расход воды (м³/день)</t>
+  </si>
+  <si>
+    <t>Подпись лица</t>
+  </si>
+  <si>
+    <t>27.05.2025</t>
+  </si>
+  <si>
+    <t>02.05.2025</t>
+  </si>
+  <si>
+    <t>32.00</t>
+  </si>
+  <si>
+    <t>200.00</t>
+  </si>
+  <si>
+    <t>Fhn</t>
   </si>
 </sst>
 </file>
@@ -386,10 +398,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -399,27 +411,36 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>30</v>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>25</v>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/back/debug_export.xlsx
+++ b/back/debug_export.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Дата измерения</t>
   </si>
@@ -28,19 +28,13 @@
     <t>Подпись лица</t>
   </si>
   <si>
-    <t>27.05.2025</t>
-  </si>
-  <si>
-    <t>02.05.2025</t>
-  </si>
-  <si>
-    <t>32.00</t>
-  </si>
-  <si>
-    <t>200.00</t>
-  </si>
-  <si>
-    <t>Fhn</t>
+    <t>09.06.2025</t>
+  </si>
+  <si>
+    <t>20.00</t>
+  </si>
+  <si>
+    <t>Артамонов В.В.</t>
   </si>
 </sst>
 </file>
@@ -398,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -423,24 +417,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/back/debug_export.xlsx
+++ b/back/debug_export.xlsx
@@ -14,27 +14,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Дата измерения</t>
-  </si>
-  <si>
-    <t>Дней эксплуатации</t>
-  </si>
-  <si>
-    <t>Расход воды (м³/день)</t>
-  </si>
-  <si>
-    <t>Подпись лица</t>
-  </si>
-  <si>
-    <t>09.06.2025</t>
-  </si>
-  <si>
-    <t>20.00</t>
-  </si>
-  <si>
-    <t>Артамонов В.В.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+  <si>
+    <t>Раздел</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Показатель</t>
+  </si>
+  <si>
+    <t>Ед. изм.</t>
+  </si>
+  <si>
+    <t>Установлено</t>
+  </si>
+  <si>
+    <t>Факт</t>
+  </si>
+  <si>
+    <t>В пределах</t>
+  </si>
+  <si>
+    <t>Превышение</t>
+  </si>
+  <si>
+    <t>Ставка</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>1. Параметры водопользования</t>
+  </si>
+  <si>
+    <t>2. Ставки платы</t>
+  </si>
+  <si>
+    <t>3. Плата за водопользование</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>1.1.2</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Забор (изъятие) водных ресурсов из поверхностного водного объекта</t>
+  </si>
+  <si>
+    <t>Забор (изъятие) водных ресурсов из поверхностного водного объекта (Qн.)</t>
+  </si>
+  <si>
+    <t>Забор (изъятие) водных ресурсов из поверхностного водного объекта (Qп.)</t>
+  </si>
+  <si>
+    <t>За забор (изъятие) водных ресурсов для населения</t>
+  </si>
+  <si>
+    <t>За забор (изъятие) водных ресурсов для предприятий</t>
+  </si>
+  <si>
+    <t>Повышающий коэффициент</t>
+  </si>
+  <si>
+    <t>За забор (изъятие) водных ресурсов (п.3.2 + п.3.3)</t>
+  </si>
+  <si>
+    <t>тыс.м3</t>
+  </si>
+  <si>
+    <t>руб/тыс.м3</t>
+  </si>
+  <si>
+    <t>руб</t>
   </si>
 </sst>
 </file>
@@ -392,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -408,19 +483,224 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>2200</v>
+      </c>
+      <c r="F3">
+        <v>70</v>
+      </c>
+      <c r="G3">
+        <v>70</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="G4">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5">
+        <v>1200</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13">
+        <v>508200</v>
+      </c>
+      <c r="F13">
+        <v>14550</v>
+      </c>
+      <c r="G13">
+        <v>14550</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>14550</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>123000</v>
+      </c>
+      <c r="F14">
+        <v>4920</v>
+      </c>
+      <c r="G14">
+        <v>4920</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>4920</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>385200</v>
+      </c>
+      <c r="F15">
+        <v>9630</v>
+      </c>
+      <c r="G15">
+        <v>9630</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9630</v>
       </c>
     </row>
   </sheetData>
